--- a/backend/templates/items_template.xlsx
+++ b/backend/templates/items_template.xlsx
@@ -430,13 +430,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -458,6 +459,11 @@
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>其他可接受答案</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>类型</t>
         </is>
       </c>
     </row>
@@ -472,13 +478,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -502,63 +509,104 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>· 类型：单词/词组/短句（todo13 #3：一列混导）；留空 = 按导入时选择的类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>英文</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t>词性</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>中文</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t>其他可接受答案</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>hello</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>感叹词</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>你好</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>喂、哈罗</t>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>类型</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>hello</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>感叹词</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>你好</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>喂、哈罗</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>单词</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>good morning</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
         <is>
           <t>早上好</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>词组</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>How are you</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>你好</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>短句</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
